--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.300284703729585</v>
+        <v>-4.30035773891821</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.145972925361427</v>
+        <v>1.145943711285977</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3765529095728913</v>
+        <v>-0.3765387469448865</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.640511485423274</v>
+        <v>2.640519983000076</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.8%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.7%</t>
+          <t>447.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.6%</t>
+          <t>-587.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.6%</t>
+          <t>-259.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-261.6%</t>
+          <t>-265.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-184.3%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.643827030740073</v>
+        <v>3.643827030740071</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.30035773891821</v>
+        <v>-4.254395595481498</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.145943711285977</v>
+        <v>1.164328568660662</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3765387469448865</v>
+        <v>-0.4153102255727366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.640519983000076</v>
+        <v>2.617257095823367</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>112.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.5%</t>
+          <t>132.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-52.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.9%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.0%</t>
+          <t>-572.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.8%</t>
+          <t>-253.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>190.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>265.8%</t>
+          <t>-179.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.5%</t>
+          <t>-241.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-184.3%</t>
+          <t>-170.1%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968859</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.099245800675061</v>
+        <v>-3.899806122012267</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.106508424250644</v>
+        <v>1.186284295715761</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2016948105647203</v>
+        <v>-0.002255131901925778</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.625546282495583</v>
+        <v>2.74521008969326</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.18224708170034</v>
+        <v>-3.982807403037546</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9116636318411855</v>
+        <v>0.991439503306303</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.220265695091894</v>
+        <v>-0.02082601642909954</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.452759471779932</v>
+        <v>2.572423278977609</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.023052809643763</v>
+        <v>-3.82361313098097</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.095491001383022</v>
+        <v>1.175266872848139</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.220265695091894</v>
+        <v>-0.02082601642909954</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.572909132499138</v>
+        <v>2.692572939696815</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660765</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.109651392624866</v>
+        <v>-3.910211713962072</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.075364594292904</v>
+        <v>1.155140465758021</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.220265695091894</v>
+        <v>-0.02082601642909954</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.587422158601461</v>
+        <v>2.707085965799138</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383421</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.071267730066715</v>
+        <v>-3.871828051403921</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.088137500658533</v>
+        <v>1.16791337212365</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1818820325337429</v>
+        <v>0.01755764612905164</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.607871797478721</v>
+        <v>2.727535604676397</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.894151400031549</v>
+        <v>-3.694711721368755</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.155713061517901</v>
+        <v>1.235488932983019</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1818820325337429</v>
+        <v>0.01755764612905164</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.604600826324023</v>
+        <v>2.724264633521699</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263899</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.864449276055256</v>
+        <v>-3.665009597392462</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.168277302870331</v>
+        <v>1.248053174335449</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1863521577490562</v>
+        <v>0.01308752091373827</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.602602142956747</v>
+        <v>2.722265950154424</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.685073854816488</v>
+        <v>-3.485634176153694</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.233814446672253</v>
+        <v>1.313590318137371</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.02957539957833755</v>
+        <v>0.1698642790844569</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.690455173165593</v>
+        <v>2.81011898036327</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.730088068337094</v>
+        <v>-3.5306483896743</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.1966162165956</v>
+        <v>1.276392088060718</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.05992429489294215</v>
+        <v>0.1395153837698523</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.65305329130842</v>
+        <v>2.772717098506097</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979535</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.997092578609529</v>
+        <v>-3.797652899946735</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.095505974825572</v>
+        <v>1.17528184629069</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2542873329358907</v>
+        <v>-0.05484765427309624</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.542127030821597</v>
+        <v>2.661790838019273</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.285879799068445</v>
+        <v>-4.08644012040565</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9791950085385071</v>
+        <v>1.058970880003625</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3553734530348911</v>
+        <v>-0.1559337743720966</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.480679280658698</v>
+        <v>2.600343087856375</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.253404212897673</v>
+        <v>-4.053964534234878</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9897852045611328</v>
+        <v>1.06956107602625</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3553734530348911</v>
+        <v>-0.1559337743720966</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.478279242213015</v>
+        <v>2.597943049410691</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.234366085190375</v>
+        <v>-4.034926406527581</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9939251748522966</v>
+        <v>1.073701046317414</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4135570643660856</v>
+        <v>-0.2141173857032911</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.439893794622543</v>
+        <v>2.55955760182022</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.25111195044675</v>
+        <v>-4.051672271783956</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.164808697688427</v>
+        <v>1.244584569153545</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4135570643660856</v>
+        <v>-0.2141173857032911</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.617475663561224</v>
+        <v>2.7371394707589</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.643827030740071</v>
+        <v>3.848875770939461</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.254395595481498</v>
+        <v>-4.103992652384748</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.164328568660662</v>
+        <v>1.224489745899362</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4153102255727366</v>
+        <v>-0.179170525694419</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.617257095823367</v>
+        <v>2.758940915750357</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.2%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.0%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.9%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>447.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-572.0%</t>
+          <t>-587.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-253.8%</t>
+          <t>-259.8%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>190.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-179.8%</t>
+          <t>265.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-241.9%</t>
+          <t>-265.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.1%</t>
+          <t>-157.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1964"/>
+  <dimension ref="A1:G1965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.899806122012267</v>
+        <v>-4.099245800675061</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186284295715761</v>
+        <v>1.106508424250644</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.002255131901925778</v>
+        <v>-0.2016948105647203</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.74521008969326</v>
+        <v>2.625546282495583</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.982807403037546</v>
+        <v>-4.18224708170034</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.991439503306303</v>
+        <v>0.9116636318411855</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.02082601642909954</v>
+        <v>-0.220265695091894</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.572423278977609</v>
+        <v>2.452759471779932</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.82361313098097</v>
+        <v>-4.023052809643763</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.175266872848139</v>
+        <v>1.095491001383022</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.02082601642909954</v>
+        <v>-0.220265695091894</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.692572939696815</v>
+        <v>2.572909132499138</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.910211713962072</v>
+        <v>-4.109651392624866</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.155140465758021</v>
+        <v>1.075364594292904</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.02082601642909954</v>
+        <v>-0.220265695091894</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.707085965799138</v>
+        <v>2.587422158601461</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.871828051403921</v>
+        <v>-4.071267730066715</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.16791337212365</v>
+        <v>1.088137500658533</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.01755764612905164</v>
+        <v>-0.1818820325337429</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.727535604676397</v>
+        <v>2.607871797478721</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.694711721368755</v>
+        <v>-3.894151400031549</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.235488932983019</v>
+        <v>1.155713061517901</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.01755764612905164</v>
+        <v>-0.1818820325337429</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.724264633521699</v>
+        <v>2.604600826324023</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.665009597392462</v>
+        <v>-3.864449276055256</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.248053174335449</v>
+        <v>1.168277302870331</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.01308752091373827</v>
+        <v>-0.1863521577490562</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.722265950154424</v>
+        <v>2.602602142956747</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.485634176153694</v>
+        <v>-3.685073854816488</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.313590318137371</v>
+        <v>1.233814446672253</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1698642790844569</v>
+        <v>-0.02957539957833755</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.81011898036327</v>
+        <v>2.690455173165593</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.5306483896743</v>
+        <v>-3.730088068337094</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.276392088060718</v>
+        <v>1.1966162165956</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1395153837698523</v>
+        <v>-0.05992429489294215</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.772717098506097</v>
+        <v>2.65305329130842</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.797652899946735</v>
+        <v>-3.997092578609529</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.17528184629069</v>
+        <v>1.095505974825572</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.05484765427309624</v>
+        <v>-0.2542873329358907</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.661790838019273</v>
+        <v>2.542127030821597</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.08644012040565</v>
+        <v>-4.285879799068445</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.058970880003625</v>
+        <v>0.9791950085385071</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1559337743720966</v>
+        <v>-0.3553734530348911</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.600343087856375</v>
+        <v>2.480679280658698</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.053964534234878</v>
+        <v>-4.253404212897673</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.06956107602625</v>
+        <v>0.9897852045611328</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1559337743720966</v>
+        <v>-0.3553734530348911</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.597943049410691</v>
+        <v>2.478279242213015</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.034926406527581</v>
+        <v>-4.234366085190375</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.073701046317414</v>
+        <v>0.9939251748522966</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2141173857032911</v>
+        <v>-0.4135570643660856</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.55955760182022</v>
+        <v>2.439893794622543</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.051672271783956</v>
+        <v>-4.25111195044675</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.244584569153545</v>
+        <v>1.164808697688427</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2141173857032911</v>
+        <v>-0.4135570643660856</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.7371394707589</v>
+        <v>2.617475663561224</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,45 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.848875770939461</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.103992652384748</v>
+        <v>-4.254395595481498</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.224489745899362</v>
+        <v>1.164328568660662</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.179170525694419</v>
+        <v>-0.4153102255727366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.758940915750357</v>
+        <v>2.617257095823367</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="2" t="n">
+        <v>45427</v>
+      </c>
+      <c r="B1965" t="n">
+        <v>3.643143693026951</v>
+      </c>
+      <c r="C1965" t="n">
+        <v>2.89562693983705</v>
+      </c>
+      <c r="D1965" t="n">
+        <v>-4.254395595481498</v>
+      </c>
+      <c r="E1965" t="n">
+        <v>1.164328568660662</v>
+      </c>
+      <c r="F1965" t="n">
+        <v>-0.4153102255727366</v>
+      </c>
+      <c r="G1965" t="n">
+        <v>2.888690736823418</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>112.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>131.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.8%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.0%</t>
+          <t>-572.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.8%</t>
+          <t>-253.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>265.8%</t>
+          <t>-63.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.5%</t>
+          <t>-250.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-141.0%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.099245800675061</v>
+        <v>-3.951425408640693</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.106508424250644</v>
+        <v>1.165636581064391</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2016948105647203</v>
+        <v>-0.05387441853035174</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.625546282495583</v>
+        <v>2.714238517716205</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.18224708170034</v>
+        <v>-4.034426689665971</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9116636318411855</v>
+        <v>0.9707917886549329</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.220265695091894</v>
+        <v>-0.0724453030575255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.452759471779932</v>
+        <v>2.541451707000554</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.023052809643763</v>
+        <v>-3.875232417609395</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.095491001383022</v>
+        <v>1.154619158196769</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.220265695091894</v>
+        <v>-0.0724453030575255</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.572909132499138</v>
+        <v>2.661601367719759</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.109651392624866</v>
+        <v>-3.961831000590498</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.075364594292904</v>
+        <v>1.134492751106651</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.220265695091894</v>
+        <v>-0.0724453030575255</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.587422158601461</v>
+        <v>2.676114393822082</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.071267730066715</v>
+        <v>-3.923447338032347</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.088137500658533</v>
+        <v>1.14726565747228</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1818820325337429</v>
+        <v>-0.03406164049937432</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.607871797478721</v>
+        <v>2.696564032699342</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.894151400031549</v>
+        <v>-3.746331007997181</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.155713061517901</v>
+        <v>1.214841218331648</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1818820325337429</v>
+        <v>-0.03406164049937432</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.604600826324023</v>
+        <v>2.693293061544644</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.864449276055256</v>
+        <v>-3.716628884020887</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.168277302870331</v>
+        <v>1.227405459684079</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1863521577490562</v>
+        <v>-0.03853176571468769</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.602602142956747</v>
+        <v>2.691294378177369</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.685073854816488</v>
+        <v>-3.537253462782119</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.233814446672253</v>
+        <v>1.292942603486001</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.02957539957833755</v>
+        <v>0.118244992456031</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.690455173165593</v>
+        <v>2.779147408386214</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.730088068337094</v>
+        <v>-3.582267676302725</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.1966162165956</v>
+        <v>1.255744373409348</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.05992429489294215</v>
+        <v>0.08789609714142638</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.65305329130842</v>
+        <v>2.741745526529041</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.997092578609529</v>
+        <v>-3.849272186575161</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.095505974825572</v>
+        <v>1.154634131639319</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2542873329358907</v>
+        <v>-0.1064669409015222</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.542127030821597</v>
+        <v>2.630819266042218</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.285879799068445</v>
+        <v>-4.138059407034076</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9791950085385071</v>
+        <v>1.038323165352255</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3553734530348911</v>
+        <v>-0.2075530610005226</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.480679280658698</v>
+        <v>2.569371515879319</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.253404212897673</v>
+        <v>-4.105583820863304</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9897852045611328</v>
+        <v>1.04891336137488</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3553734530348911</v>
+        <v>-0.2075530610005226</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.478279242213015</v>
+        <v>2.566971477433636</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.234366085190375</v>
+        <v>-4.086545693156006</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9939251748522966</v>
+        <v>1.053053331666044</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4135570643660856</v>
+        <v>-0.2657366723317171</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.439893794622543</v>
+        <v>2.528586029843164</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.25111195044675</v>
+        <v>-4.103291558412382</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.164808697688427</v>
+        <v>1.223936854502174</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4135570643660856</v>
+        <v>-0.2657366723317171</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.617475663561224</v>
+        <v>2.706167898781845</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.254395595481498</v>
+        <v>-4.106575203447129</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.164328568660662</v>
+        <v>1.223456725474409</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4153102255727366</v>
+        <v>-0.267489833538368</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.617257095823367</v>
+        <v>2.705949331043988</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.643143693026951</v>
+        <v>3.849974719149797</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.89562693983705</v>
+        <v>3.057281238938756</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.254395595481498</v>
+        <v>-4.106575203447129</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.164328568660662</v>
+        <v>1.223456725474409</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4153102255727366</v>
+        <v>-0.267489833538368</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.888690736823418</v>
+        <v>3.050345035925124</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-52.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-572.2%</t>
+          <t>-572.0%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-253.9%</t>
+          <t>-253.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>190.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-63.6%</t>
+          <t>-179.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-250.7%</t>
+          <t>-241.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-141.0%</t>
+          <t>-144.8%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.951425408640693</v>
+        <v>-3.899806122012267</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.165636581064391</v>
+        <v>1.186284295715761</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.05387441853035174</v>
+        <v>-0.002255131901925778</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.714238517716205</v>
+        <v>2.74521008969326</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.034426689665971</v>
+        <v>-3.982807403037546</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9707917886549329</v>
+        <v>0.991439503306303</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.0724453030575255</v>
+        <v>-0.02082601642909954</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.541451707000554</v>
+        <v>2.572423278977609</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.875232417609395</v>
+        <v>-3.82361313098097</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.154619158196769</v>
+        <v>1.175266872848139</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.0724453030575255</v>
+        <v>-0.02082601642909954</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.661601367719759</v>
+        <v>2.692572939696815</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.961831000590498</v>
+        <v>-3.910211713962072</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.134492751106651</v>
+        <v>1.155140465758021</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.0724453030575255</v>
+        <v>-0.02082601642909954</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.676114393822082</v>
+        <v>2.707085965799138</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.923447338032347</v>
+        <v>-3.871828051403921</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.14726565747228</v>
+        <v>1.16791337212365</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.03406164049937432</v>
+        <v>0.01755764612905164</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.696564032699342</v>
+        <v>2.727535604676397</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.746331007997181</v>
+        <v>-3.694711721368755</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.214841218331648</v>
+        <v>1.235488932983019</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.03406164049937432</v>
+        <v>0.01755764612905164</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.693293061544644</v>
+        <v>2.724264633521699</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.716628884020887</v>
+        <v>-3.665009597392462</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.227405459684079</v>
+        <v>1.248053174335449</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.03853176571468769</v>
+        <v>0.01308752091373827</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.691294378177369</v>
+        <v>2.722265950154424</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.537253462782119</v>
+        <v>-3.485634176153694</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.292942603486001</v>
+        <v>1.313590318137371</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.118244992456031</v>
+        <v>0.1698642790844569</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.779147408386214</v>
+        <v>2.81011898036327</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.582267676302725</v>
+        <v>-3.5306483896743</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.255744373409348</v>
+        <v>1.276392088060718</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.08789609714142638</v>
+        <v>0.1395153837698523</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.741745526529041</v>
+        <v>2.772717098506097</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.849272186575161</v>
+        <v>-3.797652899946735</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.154634131639319</v>
+        <v>1.17528184629069</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1064669409015222</v>
+        <v>-0.05484765427309624</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.630819266042218</v>
+        <v>2.661790838019273</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.138059407034076</v>
+        <v>-4.08644012040565</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.038323165352255</v>
+        <v>1.058970880003625</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2075530610005226</v>
+        <v>-0.1559337743720966</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.569371515879319</v>
+        <v>2.600343087856375</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.105583820863304</v>
+        <v>-4.053964534234878</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.04891336137488</v>
+        <v>1.06956107602625</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2075530610005226</v>
+        <v>-0.1559337743720966</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.566971477433636</v>
+        <v>2.597943049410691</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.086545693156006</v>
+        <v>-4.034926406527581</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.053053331666044</v>
+        <v>1.073701046317414</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2657366723317171</v>
+        <v>-0.2141173857032911</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.528586029843164</v>
+        <v>2.55955760182022</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.103291558412382</v>
+        <v>-4.051672271783956</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.223936854502174</v>
+        <v>1.244584569153545</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2657366723317171</v>
+        <v>-0.2141173857032911</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.706167898781845</v>
+        <v>2.7371394707589</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537864</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.106575203447129</v>
+        <v>-4.103992652384748</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.223456725474409</v>
+        <v>1.224489745899362</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.267489833538368</v>
+        <v>-0.179170525694419</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.705949331043988</v>
+        <v>2.758940915750357</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.849974719149797</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.057281238938756</v>
+        <v>3.01893226363339</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.106575203447129</v>
+        <v>-4.103992652384748</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.223456725474409</v>
+        <v>1.224489745899362</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.267489833538368</v>
+        <v>-0.179170525694419</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.050345035925124</v>
+        <v>3.011996060619758</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-41.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.2%</t>
+          <t>111.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-695.3%</t>
+          <t>-695.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.9%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>444.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-572.0%</t>
+          <t>-617.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.5%</t>
+          <t>-278.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-253.8%</t>
+          <t>-272.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-305.1%</t>
+          <t>-304.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>190.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-179.8%</t>
+          <t>-145.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-241.9%</t>
+          <t>-280.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.4%</t>
+          <t>-183.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-144.8%</t>
+          <t>-176.3%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-1.890215314858788</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.360477717184602</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7785641296376145</v>
+        <v>0.7815900750317027</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.584058745224433</v>
+        <v>3.585874312460887</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.22937369244731</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.217898665455643</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4394057520490924</v>
+        <v>0.4424316974431807</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.373648017977769</v>
+        <v>3.375463585214222</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.437864473898995</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.154840642613737</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.230914970597408</v>
+        <v>0.2339409159914962</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.268891838845527</v>
+        <v>3.27070740608198</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.934215290828261</v>
+        <v>-2.931189345434173</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.964399066250599</v>
+        <v>1.965609444408234</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1259288563577892</v>
+        <v>0.1289548017518775</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.213998920710324</v>
+        <v>3.215814487946777</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.426600318852358</v>
+        <v>-3.42357437345827</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.768551447084692</v>
+        <v>1.769761825242328</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3664561716663075</v>
+        <v>-0.3634302262722192</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.919674295939598</v>
+        <v>2.921489863176051</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.81178070978243</v>
+        <v>-3.808754764388342</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.613021829525527</v>
+        <v>1.614232207683162</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3664561716663075</v>
+        <v>-0.3634302262722192</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.918216834752462</v>
+        <v>2.920032401988915</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.155463483009093</v>
+        <v>-4.152437537615005</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.477317843689478</v>
+        <v>1.478528221847113</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4743622236935257</v>
+        <v>-0.4713362782994374</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.855242326990747</v>
+        <v>2.8570578942272</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.361975259896115</v>
+        <v>-4.358949314502026</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.390819191590927</v>
+        <v>1.392029569748562</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6808740005805471</v>
+        <v>-0.677848055186459</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.727441319514792</v>
+        <v>2.729256886751245</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.671209362892165</v>
+        <v>-4.668183417498077</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.268898477092766</v>
+        <v>1.270108855250401</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6808740005805471</v>
+        <v>-0.677848055186459</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.729214246215051</v>
+        <v>2.731029813451504</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.103015156041953</v>
+        <v>-5.099989210647864</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.082509047300256</v>
+        <v>1.083719425457891</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8172914970218141</v>
+        <v>-0.814265551627726</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.633696635817696</v>
+        <v>2.635512203054148</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.337709150174505</v>
+        <v>-5.334683204780417</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.976916224649325</v>
+        <v>0.9781266028069604</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.810955229792559</v>
+        <v>-0.8079292843984708</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.62578317115734</v>
+        <v>2.627598738393792</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.673371797404958</v>
+        <v>-5.670345852010869</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8412317574131092</v>
+        <v>0.8424421355707445</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.810955229792559</v>
+        <v>-0.8079292843984708</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.624363762813305</v>
+        <v>2.626179330049757</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.036998042305271</v>
+        <v>-6.033972096911183</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7022688196872253</v>
+        <v>0.7034791978448607</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9091768666596848</v>
+        <v>-0.9061509212655966</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.571918340927271</v>
+        <v>2.573733908163724</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.402125424944018</v>
+        <v>-6.399099479549929</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5554723816375584</v>
+        <v>0.5566827597951938</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.205487650958697</v>
+        <v>-1.202461705564609</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.393386385353694</v>
+        <v>2.395201952590147</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.810714202124696</v>
+        <v>-6.807688256730607</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3907984147800456</v>
+        <v>0.3920087929376814</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.614076428139376</v>
+        <v>-1.611050482745288</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.146994663060046</v>
+        <v>2.148810230296499</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.22369668626579</v>
+        <v>-7.220670740871701</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2207908535950689</v>
+        <v>0.2220012317527047</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.614076428139376</v>
+        <v>-1.611050482745288</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.142180095531507</v>
+        <v>2.14399566276796</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.640088560552788</v>
+        <v>-7.637062615158698</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05222815448914719</v>
+        <v>0.053438532646783</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.614076428139376</v>
+        <v>-1.611050482745288</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.140174146140384</v>
+        <v>2.141989713376837</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.016765571082631</v>
+        <v>-8.013739625688542</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08818395905411114</v>
+        <v>-0.08697358089647533</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.614076428139376</v>
+        <v>-1.611050482745288</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.150432836809063</v>
+        <v>2.152248404045516</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.362640393067441</v>
+        <v>-8.359614447673351</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2304343227023398</v>
+        <v>-0.229223944544704</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.614076428139376</v>
+        <v>-1.611050482745288</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.146532401954759</v>
+        <v>2.148347969191212</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.526220271251825</v>
+        <v>-8.523194325857736</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2974613539210926</v>
+        <v>-0.2962509757634568</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.614076428139376</v>
+        <v>-1.611050482745288</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.14493732200976</v>
+        <v>2.146752889246212</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.822881613062023</v>
+        <v>-8.819855667667934</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4123469147159637</v>
+        <v>-0.4111365365583279</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.682819563873254</v>
+        <v>-1.679793618479166</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.107470416498641</v>
+        <v>2.109285983735093</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.946126002277452</v>
+        <v>-8.943100056883363</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4656709749365384</v>
+        <v>-0.4644605967789026</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.682819563873254</v>
+        <v>-1.679793618479166</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.103444111964238</v>
+        <v>2.105259679200691</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.329127391020084</v>
+        <v>-9.326101445625994</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6189736317551748</v>
+        <v>-0.6177632535975395</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.682819563873254</v>
+        <v>-1.679793618479166</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.103342010642653</v>
+        <v>2.105157577879107</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.486526271233204</v>
+        <v>-9.483500325839115</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6793616678689931</v>
+        <v>-0.6781512897113573</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.840218444086376</v>
+        <v>-1.837192498692287</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.011474198486211</v>
+        <v>2.013289765722664</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.846056593737206</v>
+        <v>-9.843030648343117</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8178234935725435</v>
+        <v>-0.8166131154149081</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.840218444086376</v>
+        <v>-1.837192498692287</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.016824501784261</v>
+        <v>2.018640069020714</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.896405657191428</v>
+        <v>-9.893379711797339</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.830047098997055</v>
+        <v>-0.8288367208394192</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.890567507540598</v>
+        <v>-1.887541562146509</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.994531083668905</v>
+        <v>1.996346650905358</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.11555462526563</v>
+        <v>-10.11252867987154</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9146649356049648</v>
+        <v>-0.9134545574473294</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.109716475614795</v>
+        <v>-2.106690530220707</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.866083453446156</v>
+        <v>1.867899020682609</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.11186370030921</v>
+        <v>-10.10883775491513</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9131885656224008</v>
+        <v>-0.9119781874647654</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.109716475614795</v>
+        <v>-2.106690530220707</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.866083453446156</v>
+        <v>1.867899020682609</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.31612187563908</v>
+        <v>-10.31309593024499</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9893786386357037</v>
+        <v>-0.9881682604780684</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.237355420228784</v>
+        <v>-2.234329474834696</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.795013283796405</v>
+        <v>1.796828851032858</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.53415964727026</v>
+        <v>-10.53113370187617</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.072111192803739</v>
+        <v>-1.070900814646103</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.412126188324683</v>
+        <v>-2.409100242930595</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.694633377423302</v>
+        <v>1.696448944659754</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.46068981560281</v>
+        <v>-10.45766387020872</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.027351558643338</v>
+        <v>-1.026141180485703</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.338656356657234</v>
+        <v>-2.335630411263146</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.754086977917192</v>
+        <v>1.755902545153645</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.63581423298935</v>
+        <v>-10.63278828759526</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.082846104850439</v>
+        <v>-1.081635726692803</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.513780774043778</v>
+        <v>-2.51075482864969</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.663567548232782</v>
+        <v>1.665383115469235</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.87026632700384</v>
+        <v>-10.86724038160975</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.183846107357831</v>
+        <v>-1.182635729200195</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.513780774043778</v>
+        <v>-2.51075482864969</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.656348383331186</v>
+        <v>1.658163950567639</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.15807017154108</v>
+        <v>-11.15504422614699</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.305639835946702</v>
+        <v>-1.304429457789066</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.801584618581016</v>
+        <v>-2.798558673186928</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.476993885834867</v>
+        <v>1.47880945307132</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.21085632714141</v>
+        <v>-11.20783038174732</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.325638508348277</v>
+        <v>-1.324428130190641</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.897260105163413</v>
+        <v>-2.894234159769325</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.420704383723985</v>
+        <v>1.422519950960438</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.44288524687767</v>
+        <v>-11.43985930148358</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.415756347613666</v>
+        <v>-1.414545969456031</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.959272802351836</v>
+        <v>-2.956246856957748</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.386190494040046</v>
+        <v>1.388006061276499</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.39086973290885</v>
+        <v>-11.38784378751476</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.39095980633974</v>
+        <v>-1.389749428182105</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.959272802351836</v>
+        <v>-2.956246856957748</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.390180829726447</v>
+        <v>1.3919963969629</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.53254157463297</v>
+        <v>-11.52951562923888</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.44910376992813</v>
+        <v>-1.447893391770495</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.959272802351836</v>
+        <v>-2.956246856957748</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.388705602827705</v>
+        <v>1.390521170064158</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.48295073020814</v>
+        <v>-11.47992478481405</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.414214021993324</v>
+        <v>-1.413003643835689</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.909681957927003</v>
+        <v>-2.906656012532915</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.433513519647478</v>
+        <v>1.435329086883931</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.28379862297104</v>
+        <v>-11.44354143854447</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.347604312745168</v>
+        <v>-1.41150143897454</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.744359431977189</v>
+        <v>-2.931428230871666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.519655901570683</v>
+        <v>1.407414622233997</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.05795347025163</v>
+        <v>-11.21769628582506</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.247687178621195</v>
+        <v>-1.311584304850566</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.702432756390026</v>
+        <v>-2.889501555284502</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.55439097995919</v>
+        <v>1.442149700622504</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.93337481391404</v>
+        <v>-11.09311762948747</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.196716571530099</v>
+        <v>-1.260613697759471</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.702432756390026</v>
+        <v>-2.889501555284502</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.555530124515248</v>
+        <v>1.443288845178563</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.98627010195832</v>
+        <v>-11.14601291753175</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.215240912585705</v>
+        <v>-1.279138038815078</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.69747741030158</v>
+        <v>-2.884546209196056</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.561137106330424</v>
+        <v>1.448895826993738</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.70236137102957</v>
+        <v>-10.86210418660301</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.09594371597557</v>
+        <v>-1.159840842204942</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.69747741030158</v>
+        <v>-2.884546209196056</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.56687081056906</v>
+        <v>1.454629531232374</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.63099497841993</v>
+        <v>-10.79073779399336</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.077134421325576</v>
+        <v>-1.141031547554948</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.626111017691932</v>
+        <v>-2.813179816586408</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.599953383740984</v>
+        <v>1.487712104404298</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36715811121586</v>
+        <v>-10.52690092678929</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9814831557568557</v>
+        <v>-1.045380281986227</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.626111017691932</v>
+        <v>-2.813179816586408</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.590069902428076</v>
+        <v>1.477828623091391</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.09991631034746</v>
+        <v>-10.25965912592089</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.87642099590887</v>
+        <v>-0.9403181221382426</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.626111017691932</v>
+        <v>-2.813179816586408</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.588235341928703</v>
+        <v>1.475994062592017</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.00200927167097</v>
+        <v>-10.1617520872444</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8375584954117348</v>
+        <v>-0.9014556216411074</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.558125267831375</v>
+        <v>-2.745194066725851</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.628726476871575</v>
+        <v>1.51648519753489</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.978055730695012</v>
+        <v>-10.13779854626844</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8273085728758578</v>
+        <v>-0.8912056991052304</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.534171726855418</v>
+        <v>-2.721240525749894</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.643767107602644</v>
+        <v>1.531525828265958</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.713995792372215</v>
+        <v>-9.873738607945645</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7349449137084916</v>
+        <v>-0.7988420399378637</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.270111788532622</v>
+        <v>-2.457180587427098</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.788942754434569</v>
+        <v>1.676701475097883</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.006916168867377</v>
+        <v>-9.166658984440808</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4549000979668572</v>
+        <v>-0.5187972241962298</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.270111788532622</v>
+        <v>-2.457180587427098</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.786155720774268</v>
+        <v>1.673914441437583</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.966731870501187</v>
+        <v>-9.126474686074618</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4384827547325396</v>
+        <v>-0.5023798809619122</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.229927490166431</v>
+        <v>-2.416996289060907</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.810609923681824</v>
+        <v>1.698368644345138</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.886662074963382</v>
+        <v>-9.046404890536813</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4070880152966612</v>
+        <v>-0.4709851415260333</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.149857694628627</v>
+        <v>-2.336926493523103</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.858018622225263</v>
+        <v>1.745777342888578</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.653180852733783</v>
+        <v>-8.812923668307214</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3057710975669687</v>
+        <v>-0.3696682237963413</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.916376472399028</v>
+        <v>-2.103445271293504</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.006031784400875</v>
+        <v>1.893790505064189</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.503514461726269</v>
+        <v>-8.663257277299699</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2487967514769225</v>
+        <v>-0.3126938777062946</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.823472981156492</v>
+        <v>-2.010541780050969</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.058881668833437</v>
+        <v>1.946640389496752</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.371238988095381</v>
+        <v>-8.530981803668812</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2005190752775405</v>
+        <v>-0.2644162015069127</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.691197507525606</v>
+        <v>-1.878266306420082</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.133614439758996</v>
+        <v>2.021373160422311</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.180639313422228</v>
+        <v>-8.340382128995659</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1214641447206422</v>
+        <v>-0.1853612709500148</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.500597832852453</v>
+        <v>-1.687666631746929</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.250789305250525</v>
+        <v>2.138548025913839</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.931639514738647</v>
+        <v>-8.091382330312078</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.008957884023551355</v>
+        <v>-0.07285501025292351</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.500597832852453</v>
+        <v>-1.687666631746929</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.263695646474183</v>
+        <v>2.151454367137498</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.037229504511751</v>
+        <v>-8.196972320085182</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1791698095320116</v>
+        <v>-0.2430669357613837</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.606187822625557</v>
+        <v>-1.793256621520033</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.072365723011102</v>
+        <v>1.960124443674417</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.055964406630348</v>
+        <v>-8.215707222203779</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1381194285023639</v>
+        <v>-0.2020165547317365</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.606187822625557</v>
+        <v>-1.793256621520033</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.120910064888188</v>
+        <v>2.008668785551503</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.908024365222749</v>
+        <v>-8.06776718079618</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1988223346274918</v>
+        <v>-0.2627194608568644</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.585866906717</v>
+        <v>-1.772935705611476</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.013223691745155</v>
+        <v>1.90098241240847</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.883795728833777</v>
+        <v>-8.043538544407207</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1978448663253811</v>
+        <v>-0.2617419925547533</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.561638270328027</v>
+        <v>-1.748707069222504</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.019046887325061</v>
+        <v>1.906805607988375</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.840247322063086</v>
+        <v>-7.999990137636517</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1873861157121981</v>
+        <v>-0.2512832419415703</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.561638270328027</v>
+        <v>-1.748707069222504</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.012086275229968</v>
+        <v>1.899844995893282</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.598098928609228</v>
+        <v>-7.757841744182659</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.07606440394951175</v>
+        <v>-0.1399615301788839</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.561638270328027</v>
+        <v>-1.748707069222504</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.026548629611111</v>
+        <v>1.914307350274425</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.53486955684088</v>
+        <v>-7.69461237241431</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.0562405347829773</v>
+        <v>-0.1201376610123495</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.561638270328027</v>
+        <v>-1.748707069222504</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.021080750070306</v>
+        <v>1.90883947073362</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.411578422023749</v>
+        <v>-7.571321237597179</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.009425986845548184</v>
+        <v>-0.07332311307492034</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.438347135510897</v>
+        <v>-1.625415934405373</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.092553524971161</v>
+        <v>1.980312245634475</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.390429223120305</v>
+        <v>-7.550172038693736</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.006734670953154165</v>
+        <v>-0.05716245527621799</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.417197936607454</v>
+        <v>-1.60426673550193</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.112944022550552</v>
+        <v>2.000702743213866</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.146663781136861</v>
+        <v>-7.306406596710292</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1000215560935827</v>
+        <v>0.03612442986421049</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.417197936607454</v>
+        <v>-1.60426673550193</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.108724730897602</v>
+        <v>1.996483451560917</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.99976675341899</v>
+        <v>-7.159509568992421</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1609046811007468</v>
+        <v>0.09700755487137469</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.369539694628866</v>
+        <v>-1.556608493523342</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.139443990004771</v>
+        <v>2.027202710668086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.749916359469916</v>
+        <v>-7.008904343129177</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2535869136640789</v>
+        <v>0.1499917202003744</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.369539694628866</v>
+        <v>-1.556608493523342</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.132186064988474</v>
+        <v>2.019944785651788</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.574024267002484</v>
+        <v>-6.833012250661744</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3275428741717006</v>
+        <v>0.2239476807079965</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.369539694628866</v>
+        <v>-1.556608493523342</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.135785188509122</v>
+        <v>2.023543909172437</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.40257780398002</v>
+        <v>-6.66156578763928</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4094489654352396</v>
+        <v>0.3058537719715355</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.198093231606403</v>
+        <v>-1.385162030500879</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.251980572377154</v>
+        <v>2.139739293040468</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.177544804311197</v>
+        <v>-6.436532787970457</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4984826429190656</v>
+        <v>0.3948874494553616</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9730602319375797</v>
+        <v>-1.160129030832056</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.386020849794745</v>
+        <v>2.273779570458059</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.962910426674791</v>
+        <v>-6.221898410334051</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5890311950279461</v>
+        <v>0.4854360015642416</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7584258543011729</v>
+        <v>-0.945494653195649</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.519496277430906</v>
+        <v>2.407254998094221</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.869910385468892</v>
+        <v>-6.128898369128152</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6074254702941007</v>
+        <v>0.5038302768303966</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7584258543011729</v>
+        <v>-0.945494653195649</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.500690536214702</v>
+        <v>2.388449256878016</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.629479888664032</v>
+        <v>-5.888467872323292</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7053407456409224</v>
+        <v>0.6017455521772184</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5179953574963126</v>
+        <v>-0.7050641563907887</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.646691910922495</v>
+        <v>2.53445063158581</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.557237320492837</v>
+        <v>-5.816225304152097</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7381670867442205</v>
+        <v>0.6345718932805164</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5179953574963126</v>
+        <v>-0.7050641563907887</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.650621224757315</v>
+        <v>2.53837994542063</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.441297470867652</v>
+        <v>-5.700285454526912</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7852216105116345</v>
+        <v>0.6816264170479305</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4411736264801888</v>
+        <v>-0.6282424253746648</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.69739284728433</v>
+        <v>2.585151567947644</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.198641882444489</v>
+        <v>-5.457629866103749</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8792819171008932</v>
+        <v>0.7756867236371892</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4411736264801888</v>
+        <v>-0.6282424253746648</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.694390918504323</v>
+        <v>2.582149639167638</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.978621084407479</v>
+        <v>-5.237609068066739</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9688692733263116</v>
+        <v>0.8652740798626075</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2999537814122085</v>
+        <v>-0.4870225803066845</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.780701862555726</v>
+        <v>2.66846058321904</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.845753395344201</v>
+        <v>-5.104741379003461</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.037910531753446</v>
+        <v>0.9343153382897418</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2999537814122085</v>
+        <v>-0.4870225803066845</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.796596045357549</v>
+        <v>2.684354766020863</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.686238291824831</v>
+        <v>-4.945226275484091</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.102862417601496</v>
+        <v>0.9992672241377916</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1404386778928386</v>
+        <v>-0.3275074767873146</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.893450951909473</v>
+        <v>2.781209672572787</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.541566146725094</v>
+        <v>-4.800554130384354</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.17081937820283</v>
+        <v>1.067224184739126</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.004233467206898822</v>
+        <v>-0.1828353316875772</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.990342341530755</v>
+        <v>2.878101062194069</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.601440974082786</v>
+        <v>-4.860428957742046</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.132906938661179</v>
+        <v>1.029311745197475</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.0556413601507933</v>
+        <v>-0.2427101590452693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.940454936517566</v>
+        <v>2.82821365718088</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.514641476303778</v>
+        <v>-4.773629459963038</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.190027231095349</v>
+        <v>1.086432037631645</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.0556413601507933</v>
+        <v>-0.2427101590452693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.962855429840132</v>
+        <v>2.850614150503446</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.517111182765584</v>
+        <v>-4.776099166424844</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.189111749884038</v>
+        <v>1.085516556420334</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.05811106661259946</v>
+        <v>-0.2451798655070755</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.96144600733646</v>
+        <v>2.849204727999775</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.585481369089594</v>
+        <v>-4.844469352748854</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.172770597829137</v>
+        <v>1.069175404365432</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.04883536757638451</v>
+        <v>-0.2359041664708605</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.978018349232891</v>
+        <v>2.865777069896205</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.464064939463118</v>
+        <v>-4.723052923122378</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.211773878311618</v>
+        <v>1.108178684847914</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.04883536757638451</v>
+        <v>-0.2359041664708605</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.968455057864782</v>
+        <v>2.856213778528097</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.495058098791823</v>
+        <v>-4.754046082451083</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.024086179620523</v>
+        <v>0.9204909861568189</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.04883536757638451</v>
+        <v>-0.2359041664708605</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.793164622905169</v>
+        <v>2.680923343568483</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.319583838999353</v>
+        <v>-4.578571822658613</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.098843115529299</v>
+        <v>0.9952479220655945</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.04883536757638451</v>
+        <v>-0.2359041664708605</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.797731854896957</v>
+        <v>2.685490575560271</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.430520091640602</v>
+        <v>-4.689508075299862</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.030210643234006</v>
+        <v>0.9266154497703021</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.04883536757638451</v>
+        <v>-0.2359041664708605</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.773473883658164</v>
+        <v>2.661232604321478</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.633546669183835</v>
+        <v>-4.892534652843096</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9521313974366183</v>
+        <v>0.8485362039729143</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2518619451196179</v>
+        <v>-0.4389307440140939</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.654789322352129</v>
+        <v>2.542548043015444</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.475621070248542</v>
+        <v>-4.734609053907803</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.025474023442868</v>
+        <v>0.921878829979164</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2518619451196179</v>
+        <v>-0.4389307440140939</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.664961708784262</v>
+        <v>2.552720429447576</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.389377607222165</v>
+        <v>-4.648365590881425</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.054917679227279</v>
+        <v>0.9513224857635754</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2518619451196179</v>
+        <v>-0.4389307440140939</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.659907979358122</v>
+        <v>2.547666700021437</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.390560691873226</v>
+        <v>-4.649548675532486</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.04622022081138</v>
+        <v>0.9426250273476764</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2575049935861294</v>
+        <v>-0.4445737924806055</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.648297925722741</v>
+        <v>2.536056646386055</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.267432984879143</v>
+        <v>-4.526420968538403</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.096023176642115</v>
+        <v>0.9924279831784111</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2575049935861294</v>
+        <v>-0.4445737924806055</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.648849798755842</v>
+        <v>2.536608519419157</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.174622503428283</v>
+        <v>-4.433610487087543</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.062420061113825</v>
+        <v>0.9588248676501205</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1646945121352701</v>
+        <v>-0.3517633110297461</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.633808779517723</v>
+        <v>2.521567500181038</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.126059451207253</v>
+        <v>-4.385047434866514</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.083718757926837</v>
+        <v>0.9801235644631334</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1161314599142399</v>
+        <v>-0.3032002588087159</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.664820086774943</v>
+        <v>2.552578807438257</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.013388232971003</v>
+        <v>-4.272376216630263</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.12386295373306</v>
+        <v>1.020267760269356</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.003460241677989695</v>
+        <v>-0.1905290405724657</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.727498526228416</v>
+        <v>2.61525724689173</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.901011231788331</v>
+        <v>-4.15999921544759</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.174305050036797</v>
+        <v>1.070709856573093</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.003460241677989695</v>
+        <v>-0.1905290405724657</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.732989822059083</v>
+        <v>2.620748542722397</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.899806122012267</v>
+        <v>-4.358233784334321</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186284295715761</v>
+        <v>1.00291323078694</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.002255131901925778</v>
+        <v>-0.3887636094591963</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.74521008969326</v>
+        <v>2.513305003158898</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.982807403037546</v>
+        <v>-4.4412350653596</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.991439503306303</v>
+        <v>0.8080684383774814</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.02082601642909954</v>
+        <v>-0.4073344939863701</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.572423278977609</v>
+        <v>2.340518192443247</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.82361313098097</v>
+        <v>-4.282040793303024</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.175266872848139</v>
+        <v>0.9918958079193176</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.02082601642909954</v>
+        <v>-0.4073344939863701</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.692572939696815</v>
+        <v>2.460667853162453</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.910211713962072</v>
+        <v>-4.368639376284126</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.155140465758021</v>
+        <v>0.9717694008291995</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.02082601642909954</v>
+        <v>-0.4073344939863701</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.707085965799138</v>
+        <v>2.475180879264776</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.871828051403921</v>
+        <v>-4.330255713725975</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.16791337212365</v>
+        <v>0.9845423071948285</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.01755764612905164</v>
+        <v>-0.3689508314282189</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.727535604676397</v>
+        <v>2.495630518142035</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.694711721368755</v>
+        <v>-4.153139383690809</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.235488932983019</v>
+        <v>1.052117868054197</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.01755764612905164</v>
+        <v>-0.3689508314282189</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.724264633521699</v>
+        <v>2.492359546987337</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.665009597392462</v>
+        <v>-4.123437259714516</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.248053174335449</v>
+        <v>1.064682109406627</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.01308752091373827</v>
+        <v>-0.3734209566435323</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.722265950154424</v>
+        <v>2.490360863620062</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.485634176153694</v>
+        <v>-3.944061838475748</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.313590318137371</v>
+        <v>1.130219253208549</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1698642790844569</v>
+        <v>-0.2166441984728136</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.81011898036327</v>
+        <v>2.578213893828908</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.5306483896743</v>
+        <v>-3.989076051996354</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.276392088060718</v>
+        <v>1.093021023131896</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1395153837698523</v>
+        <v>-0.2469930937874182</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.772717098506097</v>
+        <v>2.540812011971735</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.797652899946735</v>
+        <v>-4.25608056226879</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.17528184629069</v>
+        <v>0.9919107813618677</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.05484765427309624</v>
+        <v>-0.4413561318303668</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.661790838019273</v>
+        <v>2.429885751484911</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.08644012040565</v>
+        <v>-4.544867782727705</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.058970880003625</v>
+        <v>0.875599815074803</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1559337743720966</v>
+        <v>-0.5424422519293671</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.600343087856375</v>
+        <v>2.368438001322013</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.053964534234878</v>
+        <v>-4.512392196556933</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.06956107602625</v>
+        <v>0.8861900110974288</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1559337743720966</v>
+        <v>-0.5424422519293671</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.597943049410691</v>
+        <v>2.366037962876329</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.034926406527581</v>
+        <v>-4.493354068849635</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.073701046317414</v>
+        <v>0.8903299813885925</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2141173857032911</v>
+        <v>-0.6006258632605617</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.55955760182022</v>
+        <v>2.327652515285857</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.051672271783956</v>
+        <v>-4.510099934106011</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.244584569153545</v>
+        <v>1.061213504224723</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2141173857032911</v>
+        <v>-0.6006258632605617</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.7371394707589</v>
+        <v>2.505234384224538</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.103992652384748</v>
+        <v>-4.562420314706802</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.224489745899362</v>
+        <v>1.04111868097054</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.179170525694419</v>
+        <v>-0.5656790032516895</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.758940915750357</v>
+        <v>2.527035829215995</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.849974719149797</v>
+        <v>3.393635501015943</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.01893226363339</v>
+        <v>2.703961700868885</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.103992652384748</v>
+        <v>-4.562420314706802</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.224489745899362</v>
+        <v>1.04111868097054</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.179170525694419</v>
+        <v>-0.5656790032516895</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.011996060619758</v>
+        <v>2.697025497855253</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240515.xlsx
+++ b/tame_output/ON/bt/strategyON_20240515.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>42.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-24.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-695.0%</t>
+          <t>-695.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-52.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.4%</t>
+          <t>448.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.8%</t>
+          <t>-575.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.4%</t>
+          <t>-278.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-199.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.1%</t>
+          <t>-254.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-304.8%</t>
+          <t>-305.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-145.1%</t>
+          <t>-217.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-280.6%</t>
+          <t>-256.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.3%</t>
+          <t>-183.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,27 +1471,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.3%</t>
+          <t>-178.0%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.890215314858788</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.360477717184602</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7815900750317027</v>
+        <v>0.7785641296376145</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.585874312460887</v>
+        <v>3.584058745224433</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.22937369244731</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.217898665455643</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4424316974431807</v>
+        <v>0.4394057520490924</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.375463585214222</v>
+        <v>3.373648017977769</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.437864473898995</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.154840642613737</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2339409159914962</v>
+        <v>0.230914970597408</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.27070740608198</v>
+        <v>3.268891838845527</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.931189345434173</v>
+        <v>-2.934215290828261</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.965609444408234</v>
+        <v>1.964399066250599</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1289548017518775</v>
+        <v>0.1259288563577892</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.215814487946777</v>
+        <v>3.213998920710324</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.42357437345827</v>
+        <v>-3.426600318852358</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.769761825242328</v>
+        <v>1.768551447084692</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3634302262722192</v>
+        <v>-0.3664561716663075</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.921489863176051</v>
+        <v>2.919674295939598</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.808754764388342</v>
+        <v>-3.81178070978243</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.614232207683162</v>
+        <v>1.613021829525527</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3634302262722192</v>
+        <v>-0.3664561716663075</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.920032401988915</v>
+        <v>2.918216834752462</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.152437537615005</v>
+        <v>-4.155463483009093</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.478528221847113</v>
+        <v>1.477317843689478</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4713362782994374</v>
+        <v>-0.4743622236935257</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.8570578942272</v>
+        <v>2.855242326990747</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.358949314502026</v>
+        <v>-4.361975259896115</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.392029569748562</v>
+        <v>1.390819191590927</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.677848055186459</v>
+        <v>-0.6808740005805471</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.729256886751245</v>
+        <v>2.727441319514792</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.668183417498077</v>
+        <v>-4.671209362892165</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.270108855250401</v>
+        <v>1.268898477092766</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.677848055186459</v>
+        <v>-0.6808740005805471</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.731029813451504</v>
+        <v>2.729214246215051</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.099989210647864</v>
+        <v>-5.103015156041953</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.083719425457891</v>
+        <v>1.082509047300256</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.814265551627726</v>
+        <v>-0.8172914970218141</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.635512203054148</v>
+        <v>2.633696635817696</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.334683204780417</v>
+        <v>-5.337709150174505</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9781266028069604</v>
+        <v>0.976916224649325</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8079292843984708</v>
+        <v>-0.810955229792559</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.627598738393792</v>
+        <v>2.62578317115734</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.670345852010869</v>
+        <v>-5.673371797404958</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8424421355707445</v>
+        <v>0.8412317574131092</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8079292843984708</v>
+        <v>-0.810955229792559</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.626179330049757</v>
+        <v>2.624363762813305</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.033972096911183</v>
+        <v>-6.036998042305271</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7034791978448607</v>
+        <v>0.7022688196872253</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9061509212655966</v>
+        <v>-0.9091768666596848</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.573733908163724</v>
+        <v>2.571918340927271</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.399099479549929</v>
+        <v>-6.402125424944018</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5566827597951938</v>
+        <v>0.5554723816375584</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.202461705564609</v>
+        <v>-1.205487650958697</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.395201952590147</v>
+        <v>2.393386385353694</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.807688256730607</v>
+        <v>-6.810714202124696</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3920087929376814</v>
+        <v>0.3907984147800456</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.611050482745288</v>
+        <v>-1.614076428139376</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.148810230296499</v>
+        <v>2.146994663060046</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.220670740871701</v>
+        <v>-7.22369668626579</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2220012317527047</v>
+        <v>0.2207908535950689</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.611050482745288</v>
+        <v>-1.614076428139376</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.14399566276796</v>
+        <v>2.142180095531507</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.637062615158698</v>
+        <v>-7.640088560552788</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.053438532646783</v>
+        <v>0.05222815448914719</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.611050482745288</v>
+        <v>-1.614076428139376</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.141989713376837</v>
+        <v>2.140174146140384</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.013739625688542</v>
+        <v>-8.016765571082631</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08697358089647533</v>
+        <v>-0.08818395905411114</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.611050482745288</v>
+        <v>-1.614076428139376</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.152248404045516</v>
+        <v>2.150432836809063</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.359614447673351</v>
+        <v>-8.362640393067441</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.229223944544704</v>
+        <v>-0.2304343227023398</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.611050482745288</v>
+        <v>-1.614076428139376</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.148347969191212</v>
+        <v>2.146532401954759</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.523194325857736</v>
+        <v>-8.526220271251825</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2962509757634568</v>
+        <v>-0.2974613539210926</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.611050482745288</v>
+        <v>-1.614076428139376</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.146752889246212</v>
+        <v>2.14493732200976</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.819855667667934</v>
+        <v>-8.822881613062023</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4111365365583279</v>
+        <v>-0.4123469147159637</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.679793618479166</v>
+        <v>-1.682819563873254</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.109285983735093</v>
+        <v>2.107470416498641</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.943100056883363</v>
+        <v>-8.946126002277452</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4644605967789026</v>
+        <v>-0.4656709749365384</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.679793618479166</v>
+        <v>-1.682819563873254</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.105259679200691</v>
+        <v>2.103444111964238</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.326101445625994</v>
+        <v>-9.329127391020084</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6177632535975395</v>
+        <v>-0.6189736317551748</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.679793618479166</v>
+        <v>-1.682819563873254</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.105157577879107</v>
+        <v>2.103342010642653</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.483500325839115</v>
+        <v>-9.486526271233204</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6781512897113573</v>
+        <v>-0.6793616678689931</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.837192498692287</v>
+        <v>-1.840218444086376</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.013289765722664</v>
+        <v>2.011474198486211</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.843030648343117</v>
+        <v>-9.846056593737206</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8166131154149081</v>
+        <v>-0.8178234935725435</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.837192498692287</v>
+        <v>-1.840218444086376</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.018640069020714</v>
+        <v>2.016824501784261</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.893379711797339</v>
+        <v>-9.896405657191428</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8288367208394192</v>
+        <v>-0.830047098997055</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.887541562146509</v>
+        <v>-1.890567507540598</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.996346650905358</v>
+        <v>1.994531083668905</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.11252867987154</v>
+        <v>-10.11555462526563</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9134545574473294</v>
+        <v>-0.9146649356049648</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.106690530220707</v>
+        <v>-2.109716475614795</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.867899020682609</v>
+        <v>1.866083453446156</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.10883775491513</v>
+        <v>-10.11186370030921</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9119781874647654</v>
+        <v>-0.9131885656224008</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.106690530220707</v>
+        <v>-2.109716475614795</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.867899020682609</v>
+        <v>1.866083453446156</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.31309593024499</v>
+        <v>-10.31612187563908</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9881682604780684</v>
+        <v>-0.9893786386357037</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.234329474834696</v>
+        <v>-2.237355420228784</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.796828851032858</v>
+        <v>1.795013283796405</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.53113370187617</v>
+        <v>-10.53415964727026</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.070900814646103</v>
+        <v>-1.072111192803739</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.409100242930595</v>
+        <v>-2.412126188324683</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.696448944659754</v>
+        <v>1.694633377423302</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.45766387020872</v>
+        <v>-10.46068981560281</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.026141180485703</v>
+        <v>-1.027351558643338</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.335630411263146</v>
+        <v>-2.338656356657234</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.755902545153645</v>
+        <v>1.754086977917192</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.63278828759526</v>
+        <v>-10.63581423298935</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.081635726692803</v>
+        <v>-1.082846104850439</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.51075482864969</v>
+        <v>-2.513780774043778</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.665383115469235</v>
+        <v>1.663567548232782</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.86724038160975</v>
+        <v>-10.87026632700384</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.182635729200195</v>
+        <v>-1.183846107357831</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.51075482864969</v>
+        <v>-2.513780774043778</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.658163950567639</v>
+        <v>1.656348383331186</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.15504422614699</v>
+        <v>-11.15807017154108</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.304429457789066</v>
+        <v>-1.305639835946702</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.798558673186928</v>
+        <v>-2.801584618581016</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.47880945307132</v>
+        <v>1.476993885834867</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.20783038174732</v>
+        <v>-11.21085632714141</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.324428130190641</v>
+        <v>-1.325638508348277</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.894234159769325</v>
+        <v>-2.897260105163413</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.422519950960438</v>
+        <v>1.420704383723985</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.43985930148358</v>
+        <v>-11.44288524687767</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.414545969456031</v>
+        <v>-1.415756347613666</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.956246856957748</v>
+        <v>-2.959272802351836</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.388006061276499</v>
+        <v>1.386190494040046</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.38784378751476</v>
+        <v>-11.39086973290885</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.389749428182105</v>
+        <v>-1.39095980633974</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.956246856957748</v>
+        <v>-2.959272802351836</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.3919963969629</v>
+        <v>1.390180829726447</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.52951562923888</v>
+        <v>-11.53254157463297</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.447893391770495</v>
+        <v>-1.44910376992813</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.956246856957748</v>
+        <v>-2.959272802351836</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.390521170064158</v>
+        <v>1.388705602827705</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.47992478481405</v>
+        <v>-11.48295073020814</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.413003643835689</v>
+        <v>-1.414214021993324</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.906656012532915</v>
+        <v>-2.909681957927003</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.435329086883931</v>
+        <v>1.433513519647478</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.44354143854447</v>
+        <v>-11.28379862297104</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.41150143897454</v>
+        <v>-1.347604312745168</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.931428230871666</v>
+        <v>-2.744359431977189</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.407414622233997</v>
+        <v>1.519655901570683</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.21769628582506</v>
+        <v>-11.05795347025163</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.311584304850566</v>
+        <v>-1.247687178621195</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.889501555284502</v>
+        <v>-2.702432756390026</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.442149700622504</v>
+        <v>1.55439097995919</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.09311762948747</v>
+        <v>-10.93337481391404</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.260613697759471</v>
+        <v>-1.196716571530099</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.889501555284502</v>
+        <v>-2.702432756390026</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.443288845178563</v>
+        <v>1.555530124515248</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.14601291753175</v>
+        <v>-10.98627010195832</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.279138038815078</v>
+        <v>-1.215240912585705</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.884546209196056</v>
+        <v>-2.69747741030158</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.448895826993738</v>
+        <v>1.561137106330424</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.86210418660301</v>
+        <v>-10.70236137102957</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.159840842204942</v>
+        <v>-1.09594371597557</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.884546209196056</v>
+        <v>-2.69747741030158</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.454629531232374</v>
+        <v>1.56687081056906</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.79073779399336</v>
+        <v>-10.63099497841993</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.141031547554948</v>
+        <v>-1.077134421325576</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.813179816586408</v>
+        <v>-2.626111017691932</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.487712104404298</v>
+        <v>1.599953383740984</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.52690092678929</v>
+        <v>-10.36715811121586</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.045380281986227</v>
+        <v>-0.9814831557568557</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.813179816586408</v>
+        <v>-2.626111017691932</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.477828623091391</v>
+        <v>1.590069902428076</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25965912592089</v>
+        <v>-10.09991631034746</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9403181221382426</v>
+        <v>-0.87642099590887</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.813179816586408</v>
+        <v>-2.626111017691932</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.475994062592017</v>
+        <v>1.588235341928703</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.1617520872444</v>
+        <v>-10.00200927167097</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9014556216411074</v>
+        <v>-0.8375584954117348</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.745194066725851</v>
+        <v>-2.558125267831375</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.51648519753489</v>
+        <v>1.628726476871575</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13779854626844</v>
+        <v>-9.978055730695012</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8912056991052304</v>
+        <v>-0.8273085728758578</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.721240525749894</v>
+        <v>-2.534171726855418</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.531525828265958</v>
+        <v>1.643767107602644</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.873738607945645</v>
+        <v>-9.713995792372215</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7988420399378637</v>
+        <v>-0.7349449137084916</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.457180587427098</v>
+        <v>-2.270111788532622</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.676701475097883</v>
+        <v>1.788942754434569</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.166658984440808</v>
+        <v>-9.006916168867377</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5187972241962298</v>
+        <v>-0.4549000979668572</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.457180587427098</v>
+        <v>-2.270111788532622</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.673914441437583</v>
+        <v>1.786155720774268</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.126474686074618</v>
+        <v>-8.966731870501187</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5023798809619122</v>
+        <v>-0.4384827547325396</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.416996289060907</v>
+        <v>-2.229927490166431</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.698368644345138</v>
+        <v>1.810609923681824</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.046404890536813</v>
+        <v>-8.886662074963382</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4709851415260333</v>
+        <v>-0.4070880152966612</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.336926493523103</v>
+        <v>-2.149857694628627</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.745777342888578</v>
+        <v>1.858018622225263</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.812923668307214</v>
+        <v>-8.653180852733783</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3696682237963413</v>
+        <v>-0.3057710975669687</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.103445271293504</v>
+        <v>-1.916376472399028</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.893790505064189</v>
+        <v>2.006031784400875</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.663257277299699</v>
+        <v>-8.503514461726269</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3126938777062946</v>
+        <v>-0.2487967514769225</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.010541780050969</v>
+        <v>-1.823472981156492</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.946640389496752</v>
+        <v>2.058881668833437</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.530981803668812</v>
+        <v>-8.371238988095381</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2644162015069127</v>
+        <v>-0.2005190752775405</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.878266306420082</v>
+        <v>-1.691197507525606</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.021373160422311</v>
+        <v>2.133614439758996</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.340382128995659</v>
+        <v>-8.180639313422228</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1853612709500148</v>
+        <v>-0.1214641447206422</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.687666631746929</v>
+        <v>-1.500597832852453</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.138548025913839</v>
+        <v>2.250789305250525</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.091382330312078</v>
+        <v>-7.931639514738647</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.07285501025292351</v>
+        <v>-0.008957884023551355</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.687666631746929</v>
+        <v>-1.500597832852453</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.151454367137498</v>
+        <v>2.263695646474183</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.196972320085182</v>
+        <v>-8.037229504511751</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2430669357613837</v>
+        <v>-0.1791698095320116</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.793256621520033</v>
+        <v>-1.606187822625557</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.960124443674417</v>
+        <v>2.072365723011102</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.215707222203779</v>
+        <v>-7.901845096317865</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2020165547317365</v>
+        <v>-0.07647170437737039</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.793256621520033</v>
+        <v>-1.512624404420407</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.008668785551503</v>
+        <v>2.177048115811279</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.06776718079618</v>
+        <v>-7.753905054910265</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2627194608568644</v>
+        <v>-0.1371746105024982</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.772935705611476</v>
+        <v>-1.49230348851185</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.90098241240847</v>
+        <v>2.069361742668246</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.043538544407207</v>
+        <v>-7.729676418521293</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2617419925547533</v>
+        <v>-0.1361971422003876</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.748707069222504</v>
+        <v>-1.468074852122877</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.906805607988375</v>
+        <v>2.075184938248151</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.999990137636517</v>
+        <v>-7.686128011750602</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2512832419415703</v>
+        <v>-0.1257383915872046</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.748707069222504</v>
+        <v>-1.468074852122877</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.899844995893282</v>
+        <v>2.068224326153058</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.757841744182659</v>
+        <v>-7.443979618296744</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1399615301788839</v>
+        <v>-0.01441667982451822</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.748707069222504</v>
+        <v>-1.468074852122877</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.914307350274425</v>
+        <v>2.082686680534201</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.69461237241431</v>
+        <v>-7.380750246528396</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1201376610123495</v>
+        <v>0.005407189342016228</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.748707069222504</v>
+        <v>-1.468074852122877</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.90883947073362</v>
+        <v>2.077218800993396</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.571321237597179</v>
+        <v>-7.257459111711265</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.07332311307492034</v>
+        <v>0.05222173727944535</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.625415934405373</v>
+        <v>-1.344783717305747</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.980312245634475</v>
+        <v>2.148691575894251</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.550172038693736</v>
+        <v>-7.236309912807822</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.05716245527621799</v>
+        <v>0.0683823950781477</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.60426673550193</v>
+        <v>-1.323634518402304</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.000702743213866</v>
+        <v>2.169082073473642</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.306406596710292</v>
+        <v>-6.992544470824377</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.03612442986421049</v>
+        <v>0.1616692802185762</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.60426673550193</v>
+        <v>-1.323634518402304</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.996483451560917</v>
+        <v>2.164862781820693</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.159509568992421</v>
+        <v>-6.845647443106508</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09700755487137469</v>
+        <v>0.2225524052257404</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.556608493523342</v>
+        <v>-1.275976276423715</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.027202710668086</v>
+        <v>2.195582040927861</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.008904343129177</v>
+        <v>-6.595797049157433</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1499917202003744</v>
+        <v>0.315234637789072</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.556608493523342</v>
+        <v>-1.275976276423715</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.019944785651788</v>
+        <v>2.188324115911564</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.833012250661744</v>
+        <v>-6.419904956690001</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2239476807079965</v>
+        <v>0.3891905982966937</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.556608493523342</v>
+        <v>-1.275976276423715</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.023543909172437</v>
+        <v>2.191923239432212</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.66156578763928</v>
+        <v>-6.248458493667537</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3058537719715355</v>
+        <v>0.4710966895602327</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.385162030500879</v>
+        <v>-1.104529813401252</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.139739293040468</v>
+        <v>2.308118623300244</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.436532787970457</v>
+        <v>-6.023425493998714</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3948874494553616</v>
+        <v>0.5601303670440592</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.160129030832056</v>
+        <v>-0.8794968137324296</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.273779570458059</v>
+        <v>2.442158900717835</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.221898410334051</v>
+        <v>-5.808791116362308</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4854360015642416</v>
+        <v>0.6506789191529392</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.945494653195649</v>
+        <v>-0.6648624360960228</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.407254998094221</v>
+        <v>2.575634328353996</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.128898369128152</v>
+        <v>-5.715791075156409</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5038302768303966</v>
+        <v>0.6690731944190942</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.945494653195649</v>
+        <v>-0.6648624360960228</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.388449256878016</v>
+        <v>2.556828587137792</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.888467872323292</v>
+        <v>-5.475360578351549</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6017455521772184</v>
+        <v>0.7669884697659155</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7050641563907887</v>
+        <v>-0.4244319392911625</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.53445063158581</v>
+        <v>2.702829961845585</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.816225304152097</v>
+        <v>-5.403118010180354</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6345718932805164</v>
+        <v>0.7998148108692136</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7050641563907887</v>
+        <v>-0.4244319392911625</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.53837994542063</v>
+        <v>2.706759275680406</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.700285454526912</v>
+        <v>-5.287178160555169</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6816264170479305</v>
+        <v>0.8468693346366276</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6282424253746648</v>
+        <v>-0.3476102082750386</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.585151567947644</v>
+        <v>2.75353089820742</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.457629866103749</v>
+        <v>-5.044522572132006</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7756867236371892</v>
+        <v>0.9409296412258863</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6282424253746648</v>
+        <v>-0.3476102082750386</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.582149639167638</v>
+        <v>2.750528969427413</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.237609068066739</v>
+        <v>-4.824501774094996</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8652740798626075</v>
+        <v>1.030516997451305</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4870225803066845</v>
+        <v>-0.2063903632070584</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.66846058321904</v>
+        <v>2.836839913478816</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.104741379003461</v>
+        <v>-4.691634085031718</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9343153382897418</v>
+        <v>1.099558255878439</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4870225803066845</v>
+        <v>-0.2063903632070584</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.684354766020863</v>
+        <v>2.852734096280639</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.945226275484091</v>
+        <v>-4.532118981512348</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9992672241377916</v>
+        <v>1.164510141726489</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3275074767873146</v>
+        <v>-0.04687525968768846</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.781209672572787</v>
+        <v>2.949589002832563</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.800554130384354</v>
+        <v>-4.387446836412611</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.067224184739126</v>
+        <v>1.232467102327824</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1828353316875772</v>
+        <v>0.09779688541204895</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.878101062194069</v>
+        <v>3.046480392453845</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.860428957742046</v>
+        <v>-4.447321663770303</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.029311745197475</v>
+        <v>1.194554662786173</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2427101590452693</v>
+        <v>0.03792205805435683</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.82821365718088</v>
+        <v>2.996592987440656</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.773629459963038</v>
+        <v>-4.360522165991295</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.086432037631645</v>
+        <v>1.251674955220342</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2427101590452693</v>
+        <v>0.03792205805435683</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.850614150503446</v>
+        <v>3.018993480763222</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.776099166424844</v>
+        <v>-4.362991872453101</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.085516556420334</v>
+        <v>1.250759474009032</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2451798655070755</v>
+        <v>0.03545235159255067</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.849204727999775</v>
+        <v>3.01758405825955</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.844469352748854</v>
+        <v>-4.431362058777111</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.069175404365432</v>
+        <v>1.23441832195413</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2359041664708605</v>
+        <v>0.04472805062876561</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.865777069896205</v>
+        <v>3.034156400155981</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.723052923122378</v>
+        <v>-4.309945629150635</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.108178684847914</v>
+        <v>1.273421602436612</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2359041664708605</v>
+        <v>0.04472805062876561</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.856213778528097</v>
+        <v>3.024593108787872</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.754046082451083</v>
+        <v>-4.34093878847934</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9204909861568189</v>
+        <v>1.085733903745516</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2359041664708605</v>
+        <v>0.04472805062876561</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.680923343568483</v>
+        <v>2.849302673828259</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.578571822658613</v>
+        <v>-4.16546452868687</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9952479220655945</v>
+        <v>1.160490839654292</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2359041664708605</v>
+        <v>0.04472805062876561</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.685490575560271</v>
+        <v>2.853869905820047</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.689508075299862</v>
+        <v>-4.276400781328119</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9266154497703021</v>
+        <v>1.091858367358999</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2359041664708605</v>
+        <v>0.04472805062876561</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.661232604321478</v>
+        <v>2.829611934581254</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.892534652843096</v>
+        <v>-4.479427358871352</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8485362039729143</v>
+        <v>1.013779121561612</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4389307440140939</v>
+        <v>-0.1582985269144678</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.542548043015444</v>
+        <v>2.710927373275219</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.734609053907803</v>
+        <v>-4.321501759936059</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.921878829979164</v>
+        <v>1.087121747567861</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4389307440140939</v>
+        <v>-0.1582985269144678</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.552720429447576</v>
+        <v>2.721099759707352</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.648365590881425</v>
+        <v>-4.235258296909682</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9513224857635754</v>
+        <v>1.116565403352273</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4389307440140939</v>
+        <v>-0.1582985269144678</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.547666700021437</v>
+        <v>2.716046030281212</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.649548675532486</v>
+        <v>-4.236441381560743</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9426250273476764</v>
+        <v>1.107867944936374</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4445737924806055</v>
+        <v>-0.1639415753809793</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.536056646386055</v>
+        <v>2.704435976645831</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.526420968538403</v>
+        <v>-4.11331367456666</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9924279831784111</v>
+        <v>1.157670900767108</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4445737924806055</v>
+        <v>-0.1639415753809793</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.536608519419157</v>
+        <v>2.704987849678932</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.433610487087543</v>
+        <v>-4.0205031931158</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9588248676501205</v>
+        <v>1.124067785238818</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3517633110297461</v>
+        <v>-0.07113109393011996</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.521567500181038</v>
+        <v>2.689946830440813</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.385047434866514</v>
+        <v>-3.97194014089477</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9801235644631334</v>
+        <v>1.145366482051831</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3032002588087159</v>
+        <v>-0.02256804170908977</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.552578807438257</v>
+        <v>2.720958137698033</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.272376216630263</v>
+        <v>-3.85926892265852</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.020267760269356</v>
+        <v>1.185510677858054</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1905290405724657</v>
+        <v>0.09010317652716043</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.61525724689173</v>
+        <v>2.783636577151506</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.15999921544759</v>
+        <v>-3.746891921475847</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.070709856573093</v>
+        <v>1.23595277416179</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1905290405724657</v>
+        <v>0.09010317652716043</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.620748542722397</v>
+        <v>2.789127872982173</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.358233784334321</v>
+        <v>-3.945126490362578</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.00291323078694</v>
+        <v>1.168156148375637</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3887636094591963</v>
+        <v>-0.1081313923595701</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.513305003158898</v>
+        <v>2.681684333418674</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.4412350653596</v>
+        <v>-3.991561250942971</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8080684383774814</v>
+        <v>0.987937964144133</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4073344939863701</v>
+        <v>-0.1612892747034492</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.340518192443247</v>
+        <v>2.488145324012999</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.282040793303024</v>
+        <v>-3.832366978886395</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9918958079193176</v>
+        <v>1.171765333685969</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4073344939863701</v>
+        <v>-0.1612892747034492</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.460667853162453</v>
+        <v>2.608294984732205</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.368639376284126</v>
+        <v>-3.918965561867497</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9717694008291995</v>
+        <v>1.151638926595851</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4073344939863701</v>
+        <v>-0.1612892747034492</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.475180879264776</v>
+        <v>2.622808010834528</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.330255713725975</v>
+        <v>-3.880581899309346</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9845423071948285</v>
+        <v>1.16441183296148</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3689508314282189</v>
+        <v>-0.122905612145298</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.495630518142035</v>
+        <v>2.643257649711788</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.153139383690809</v>
+        <v>-3.70346556927418</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.052117868054197</v>
+        <v>1.231987393820849</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3689508314282189</v>
+        <v>-0.122905612145298</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.492359546987337</v>
+        <v>2.63998667855709</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.123437259714516</v>
+        <v>-3.673763445297887</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.064682109406627</v>
+        <v>1.244551635173279</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3734209566435323</v>
+        <v>-0.1273757373606114</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.490360863620062</v>
+        <v>2.637987995189814</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.944061838475748</v>
+        <v>-3.494388024059119</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.130219253208549</v>
+        <v>1.3100887789752</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2166441984728136</v>
+        <v>0.02940102081010731</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.578213893828908</v>
+        <v>2.72584102539866</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.989076051996354</v>
+        <v>-3.539402237579725</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.093021023131896</v>
+        <v>1.272890548898548</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2469930937874182</v>
+        <v>-0.0009478745044972925</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.540812011971735</v>
+        <v>2.688439143541487</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.25608056226879</v>
+        <v>-3.806406747852161</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9919107813618677</v>
+        <v>1.171780307128519</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4413561318303668</v>
+        <v>-0.1953109125474459</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.429885751484911</v>
+        <v>2.577512883054664</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.544867782727705</v>
+        <v>-4.095193968311076</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.875599815074803</v>
+        <v>1.055469340841455</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5424422519293671</v>
+        <v>-0.2963970326464462</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.368438001322013</v>
+        <v>2.516065132891765</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.512392196556933</v>
+        <v>-4.062718382140304</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8861900110974288</v>
+        <v>1.06605953686408</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5424422519293671</v>
+        <v>-0.2963970326464462</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.366037962876329</v>
+        <v>2.513665094446082</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.493354068849635</v>
+        <v>-4.043680254433006</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8903299813885925</v>
+        <v>1.070199507155244</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6006258632605617</v>
+        <v>-0.3545806439776408</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.327652515285857</v>
+        <v>2.47527964685561</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.510099934106011</v>
+        <v>-4.060426119689382</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.061213504224723</v>
+        <v>1.241083029991375</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6006258632605617</v>
+        <v>-0.3545806439776408</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.505234384224538</v>
+        <v>2.652861515794291</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.562420314706802</v>
+        <v>-4.112746500290173</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.04111868097054</v>
+        <v>1.220988206737192</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5656790032516895</v>
+        <v>-0.3196337839687686</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.527035829215995</v>
+        <v>2.674662960785747</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.393635501015943</v>
+        <v>3.709223445420776</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.703961700868885</v>
+        <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.562420314706802</v>
+        <v>-4.142177946415754</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.04111868097054</v>
+        <v>1.215224158683885</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5656790032516895</v>
+        <v>-0.3196337839687686</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.697025497855253</v>
+        <v>2.680671491182673</v>
       </c>
     </row>
   </sheetData>
